--- a/E/WBC01N.xlsx
+++ b/E/WBC01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="48">
   <si>
     <t/>
   </si>
@@ -547,17 +547,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,8 +577,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -593,11 +600,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -613,11 +620,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -633,11 +640,11 @@
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -653,11 +660,11 @@
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -673,11 +680,11 @@
       <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -693,11 +700,11 @@
       <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -713,11 +720,11 @@
       <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -733,11 +740,11 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -753,11 +760,11 @@
       <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -773,11 +780,11 @@
       <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -793,11 +800,11 @@
       <c r="E12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -813,11 +820,11 @@
       <c r="E13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -833,11 +840,11 @@
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
@@ -853,11 +860,11 @@
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -873,11 +880,11 @@
       <c r="E16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
@@ -893,11 +900,11 @@
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
@@ -913,11 +920,11 @@
       <c r="E18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -933,11 +940,11 @@
       <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -953,11 +960,11 @@
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -973,7 +980,7 @@
       <c r="E21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/WBC01N.xlsx
+++ b/E/WBC01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="48">
   <si>
     <t/>
   </si>
@@ -547,18 +547,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,14 +576,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -600,11 +593,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -620,11 +613,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -640,11 +633,11 @@
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -660,11 +653,11 @@
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -680,11 +673,11 @@
       <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -700,11 +693,11 @@
       <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -720,11 +713,11 @@
       <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -740,11 +733,11 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -760,11 +753,11 @@
       <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -780,11 +773,11 @@
       <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -800,11 +793,11 @@
       <c r="E12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -820,11 +813,11 @@
       <c r="E13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -840,11 +833,11 @@
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
@@ -860,11 +853,11 @@
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -880,11 +873,11 @@
       <c r="E16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
@@ -900,11 +893,11 @@
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
@@ -920,11 +913,11 @@
       <c r="E18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -940,11 +933,11 @@
       <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -960,11 +953,11 @@
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -980,7 +973,7 @@
       <c r="E21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>5</v>
       </c>
     </row>
